--- a/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - DONA JOSEFA CAMPUS.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - DONA JOSEFA CAMPUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F0F46D3-D1B4-4CBF-936C-A0C918EC87A0}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB04B7B-F78A-4C57-B945-55B8E8B588C1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="15">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3712,10 +3712,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="15">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="15">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5399,12 +5399,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49 E8:E12 E14:E19 E21:E29 E31:E39 E51:E59 E2:E6 E61:E69 E71:E79 E81:E89 E91:E95 E96:E97" xr:uid="{BD978047-A468-4418-8814-468F13E5EF5A}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5416,7 +5419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5710,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5779,7 +5782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5848,7 +5851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5917,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5986,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6055,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6124,7 +6127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6193,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6206,7 +6209,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6275,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6344,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6413,7 +6416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6482,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6551,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6620,7 +6623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6689,7 +6692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6758,7 +6761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6772,7 +6775,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6841,7 +6844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6910,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6979,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7048,7 +7051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7117,7 +7120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7186,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7255,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7324,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7393,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7407,7 +7410,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7476,7 +7479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7545,7 +7548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7614,7 +7617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7683,7 +7686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7752,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7821,7 +7824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7959,7 +7962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8028,7 +8031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8042,7 +8045,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8111,7 +8114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8180,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8249,7 +8252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8318,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8387,7 +8390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8456,7 +8459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8525,7 +8528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8594,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8663,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8677,7 +8680,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8746,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8815,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8884,7 +8887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8953,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9022,7 +9025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9091,7 +9094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9160,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9229,7 +9232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9312,7 +9315,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9381,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9450,7 +9453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9519,7 +9522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9588,7 +9591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9657,7 +9660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9726,7 +9729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9795,7 +9798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9864,7 +9867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9933,7 +9936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9947,7 +9950,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10016,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10085,7 +10088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10154,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10223,7 +10226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10292,7 +10295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10361,7 +10364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10430,7 +10433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10499,7 +10502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10568,7 +10571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10582,7 +10585,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10651,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10720,7 +10723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10789,7 +10792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10858,7 +10861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10927,7 +10930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10996,7 +10999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11065,7 +11068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11134,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11203,7 +11206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11217,7 +11220,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11286,7 +11289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11355,7 +11358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11424,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11493,7 +11496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11562,7 +11565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11631,7 +11634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11700,7 +11703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11769,7 +11772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11839,6 +11842,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+      <c r="F102"/>
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11990,7 +11994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12128,7 +12132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12335,7 +12339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12404,7 +12408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12415,7 +12419,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12477,7 +12481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12539,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12601,7 +12605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12663,7 +12667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12725,7 +12729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12787,7 +12791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12849,7 +12853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12911,7 +12915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12973,7 +12977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13035,7 +13039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13097,7 +13101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13159,7 +13163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13221,7 +13225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13283,7 +13287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13345,13 +13349,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -13366,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13378,7 +13382,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13393,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13404,190 +13408,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:Q126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D93:F101 D83:F91 D73:F81 D103:F110 D112:F127 K6:L12 K53:L61 K43:L51 K33:L41 K23:L31 K14:L21 K63:L71 K93:L101 K83:L91 K73:L81 K103:L110 K112:L127 N5:R12 Q63:R71 Q93:R101 Q83:R91 Q73:R81 Q53:R61 Q43:R51 Q33:R41 Q23:R31 Q14:R21 Q103:R110 R112:R127 T5:X12 W63:X71 W93:X101 W83:X91 W73:X81 W53:X61 W43:X51 W33:X41 W23:X31 W14:X21 W103:X110 W112:X127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13597,15 +13421,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F93:F101 F83:F91 F63:F71 F73:F81 F103:F110 F112:F127 L53:L61 L43:L51 L33:L41 L23:L31 L5:L12 L14:L21 L93:L101 L83:L91 L63:L71 L73:L81 L103:L110 L112:L127 R73:R81 R93:R101 R83:R91 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R5:R12 R14:R21 R103:R110 R112:R127 X73:X81 X93:X101 X83:X91 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{220463FE-6974-4E9A-84D3-B5183FE7DF4D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13835,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13904,7 +13731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13973,7 +13800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14042,7 +13869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14111,7 +13938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14180,7 +14007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14249,7 +14076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14318,8 +14145,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14388,7 +14215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14457,7 +14284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14526,7 +14353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14595,7 +14422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14664,7 +14491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14733,7 +14560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14802,7 +14629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14871,8 +14698,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14941,7 +14768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15010,7 +14837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15079,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15148,7 +14975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15217,7 +15044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15286,7 +15113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15355,7 +15182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15424,7 +15251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15493,8 +15320,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15563,7 +15390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15632,7 +15459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15701,7 +15528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15770,7 +15597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15839,7 +15666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15908,7 +15735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15977,7 +15804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16046,7 +15873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16115,7 +15942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16184,7 +16011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16253,8 +16080,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16323,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16392,7 +16219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16461,7 +16288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16530,7 +16357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16599,7 +16426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16668,7 +16495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16737,7 +16564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16806,7 +16633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16875,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16944,7 +16771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17013,8 +16840,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17083,7 +16910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17152,7 +16979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17221,7 +17048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17290,7 +17117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17359,7 +17186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17428,7 +17255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17497,7 +17324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17566,7 +17393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17635,7 +17462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17704,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17843,7 +17670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17912,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17981,7 +17808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18050,7 +17877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18119,7 +17946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18188,7 +18015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18257,7 +18084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18326,7 +18153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18395,7 +18222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18464,7 +18291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18533,8 +18360,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18603,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18672,7 +18499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18741,7 +18568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18810,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18879,7 +18706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18948,7 +18775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19017,7 +18844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19086,7 +18913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19155,7 +18982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19224,7 +19051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19293,8 +19120,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19363,7 +19190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19432,7 +19259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19501,7 +19328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19570,7 +19397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19639,7 +19466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19708,7 +19535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19777,7 +19604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19846,7 +19673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19915,7 +19742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19984,7 +19811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20053,8 +19880,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20123,7 +19950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20192,7 +20019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20261,7 +20088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20330,7 +20157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20399,7 +20226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20468,7 +20295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20537,7 +20364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20606,7 +20433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20675,7 +20502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20883,7 +20710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20952,7 +20779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21021,7 +20848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21090,7 +20917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21159,7 +20986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21228,7 +21055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21297,7 +21124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -22060,7 +21887,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D55:F65 D43:F53 D31:F41 D21:F29 D12:F19 D67:F77 D103:F113 D91:F101 D79:F89 D115:F122 H3:L10 H67:L77 H103:L113 H91:L101 H79:L89 H43:L53 H31:L41 H21:L29 H12:L19 H55:L65 H115:L122 P2:R10 N12:R19 N55:R65 N43:R53 N31:R41 N21:R29 N67:R77 N103:R113 N91:R101 N79:R89 N115:R122 V2:X10 T67:X77 T103:X113 T91:X101 T79:X89 T55:X65 T43:X53 T31:X41 T21:X29 T12:X19 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22070,12 +21897,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F31:F41 F21:F29 F3:F10 F12:F19 F103:F113 F91:F101 F67:F77 F79:F89 F115:F122 L79:L89 L103:L113 L91:L101 L67:L77 L12:L19 L31:L41 L21:L29 L3:L10 L43:L53 L55:L65 L115:L122 R3:R10 R55:R65 R43:R53 R31:R41 R12:R19 R21:R29 R103:R113 R91:R101 R67:R77 R79:R89 R115:R122 X79:X89 X103:X113 X91:X101 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X3:X10 X12:X19" xr:uid="{0EC60239-38BD-4FA7-9FB4-C4012ED5EBA9}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
